--- a/Data Files/7.1. Credit Transfer - Success Partisipan Debitur ke Partisipan Kreditur.xlsx
+++ b/Data Files/7.1. Credit Transfer - Success Partisipan Debitur ke Partisipan Kreditur.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chindy\Chindy\BIFAST\Revamp\Automation\Komi-API BIFAST 2.0\Komi-API Now\Komi-API\Data Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wirafidi/git/Bifast-2.0-Katalon/Data Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84B5DCC-D47A-4BF4-9C0F-B3992943DD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CC6183-50E8-FC44-9746-165E88946887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
+    <workbookView xWindow="6120" yWindow="6280" windowWidth="23260" windowHeight="12460" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="66">
-  <si>
-    <t>Authorization</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t>Content_Type</t>
   </si>
@@ -36,21 +33,12 @@
     <t>transactionId</t>
   </si>
   <si>
-    <t>transactionCode</t>
-  </si>
-  <si>
-    <t>cid</t>
-  </si>
-  <si>
     <t>channelType</t>
   </si>
   <si>
     <t>application/json</t>
   </si>
   <si>
-    <t>Basic YmlmYXN0MjAyNTpiaWZhc3QyMDI1</t>
-  </si>
-  <si>
     <t>branchInput</t>
   </si>
   <si>
@@ -84,9 +72,6 @@
     <t>chargeBearerCode</t>
   </si>
   <si>
-    <t>userInput</t>
-  </si>
-  <si>
     <t>0502</t>
   </si>
   <si>
@@ -105,12 +90,6 @@
     <t>DEBT</t>
   </si>
   <si>
-    <t>A002</t>
-  </si>
-  <si>
-    <t>310000</t>
-  </si>
-  <si>
     <t>branchCode</t>
   </si>
   <si>
@@ -189,18 +168,6 @@
     <t>paymentInformation</t>
   </si>
   <si>
-    <t>channelRef</t>
-  </si>
-  <si>
-    <t>MBL-M001-</t>
-  </si>
-  <si>
-    <t>MBL</t>
-  </si>
-  <si>
-    <t>FAST-JSON-MBL-01</t>
-  </si>
-  <si>
     <t>TESTING MANUAL</t>
   </si>
   <si>
@@ -222,7 +189,16 @@
     <t>Test transfer</t>
   </si>
   <si>
-    <t>250826103260</t>
+    <t>250826103360</t>
+  </si>
+  <si>
+    <t>institutionBic</t>
+  </si>
+  <si>
+    <t>BMRIIDJA</t>
+  </si>
+  <si>
+    <t>KOMI-MOBILE</t>
   </si>
 </sst>
 </file>
@@ -302,9 +278,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -342,7 +318,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -448,7 +424,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -590,7 +566,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -598,13 +574,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA04E825-9583-433C-8FA8-025B5A2F7BE7}">
-  <dimension ref="A1:AI2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AE2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="35" width="20.5546875" customWidth="1"/>
+    <col min="1" max="31" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -612,210 +588,186 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="L2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="3" t="s">
+      <c r="N2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O1" s="3" t="s">
+      <c r="O2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y1" s="3" t="s">
+      <c r="V2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AB2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AA1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AC2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AD2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE2" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="AH1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/7.1. Credit Transfer - Success Partisipan Debitur ke Partisipan Kreditur.xlsx
+++ b/Data Files/7.1. Credit Transfer - Success Partisipan Debitur ke Partisipan Kreditur.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wirafidi/git/Bifast-2.0-Katalon/Data Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hutap\git\Katalon\Data Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CC6183-50E8-FC44-9746-165E88946887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784B597A-694E-40C3-B265-F6FC278B85D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="6280" windowWidth="23260" windowHeight="12460" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="66">
   <si>
     <t>Content_Type</t>
   </si>
@@ -198,7 +198,31 @@
     <t>BMRIIDJA</t>
   </si>
   <si>
-    <t>KOMI-MOBILE</t>
+    <t>172.24.281.24</t>
+  </si>
+  <si>
+    <t>09864ADCASA</t>
+  </si>
+  <si>
+    <t>-6.1617169</t>
+  </si>
+  <si>
+    <t>106.6643946</t>
+  </si>
+  <si>
+    <t>X_IP_ADDRESS</t>
+  </si>
+  <si>
+    <t>X_DEVICE_ID</t>
+  </si>
+  <si>
+    <t>X_LATITUDE</t>
+  </si>
+  <si>
+    <t>X_LONGITUDE</t>
+  </si>
+  <si>
+    <t>KOMIMOBILE</t>
   </si>
 </sst>
 </file>
@@ -255,11 +279,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -278,9 +303,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -318,7 +343,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -424,7 +449,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -566,7 +591,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -574,13 +599,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA04E825-9583-433C-8FA8-025B5A2F7BE7}">
-  <dimension ref="A1:AE2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AI2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="31" width="20.5" customWidth="1"/>
+    <col min="1" max="31" width="20.44140625" customWidth="1"/>
+    <col min="32" max="35" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -674,8 +700,20 @@
       <c r="AE1" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="AF1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AH1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI1" s="3" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -686,7 +724,7 @@
         <v>56</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>22</v>
@@ -768,6 +806,18 @@
       </c>
       <c r="AE2" s="2" t="s">
         <v>53</v>
+      </c>
+      <c r="AF2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI2" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/7.1. Credit Transfer - Success Partisipan Debitur ke Partisipan Kreditur.xlsx
+++ b/Data Files/7.1. Credit Transfer - Success Partisipan Debitur ke Partisipan Kreditur.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hutap\git\Katalon\Data Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784B597A-694E-40C3-B265-F6FC278B85D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF72434-7EDA-4223-B5DC-646FB463C142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
   </bookViews>
@@ -111,9 +111,6 @@
     <t>debitedCityCode</t>
   </si>
   <si>
-    <t>0191</t>
-  </si>
-  <si>
     <t>debitedId</t>
   </si>
   <si>
@@ -132,9 +129,6 @@
     <t>creditedAccountName</t>
   </si>
   <si>
-    <t>KU000022000462138</t>
-  </si>
-  <si>
     <t>creditedAccountNumber</t>
   </si>
   <si>
@@ -156,9 +150,6 @@
     <t>creditedId</t>
   </si>
   <si>
-    <t>123456</t>
-  </si>
-  <si>
     <t>creditedResidentStatus</t>
   </si>
   <si>
@@ -168,30 +159,18 @@
     <t>paymentInformation</t>
   </si>
   <si>
-    <t>TESTING MANUAL</t>
-  </si>
-  <si>
-    <t>3273182301870002</t>
-  </si>
-  <si>
     <t>400000001</t>
   </si>
   <si>
     <t>MEGAIDJA</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
     <t>1000</t>
   </si>
   <si>
     <t>Test transfer</t>
   </si>
   <si>
-    <t>250826103360</t>
-  </si>
-  <si>
     <t>institutionBic</t>
   </si>
   <si>
@@ -223,6 +202,27 @@
   </si>
   <si>
     <t>KOMIMOBILE</t>
+  </si>
+  <si>
+    <t>250828103360</t>
+  </si>
+  <si>
+    <t>ANDRY SYAPUTRA</t>
+  </si>
+  <si>
+    <t>0111</t>
+  </si>
+  <si>
+    <t>3273182301870001</t>
+  </si>
+  <si>
+    <t>SIMULATOR</t>
+  </si>
+  <si>
+    <t>32750411111100122</t>
+  </si>
+  <si>
+    <t>2000.00</t>
   </si>
 </sst>
 </file>
@@ -614,7 +614,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
@@ -641,31 +641,31 @@
         <v>27</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="N1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="S1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="T1" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="U1" s="3" t="s">
         <v>8</v>
@@ -674,10 +674,10 @@
         <v>7</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Y1" s="3" t="s">
         <v>13</v>
@@ -698,19 +698,19 @@
         <v>14</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
@@ -718,13 +718,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>22</v>
@@ -736,55 +736,55 @@
         <v>22</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="T2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="U2" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Y2" s="2" t="s">
         <v>19</v>
@@ -793,10 +793,10 @@
         <v>17</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="AC2" s="2" t="s">
         <v>18</v>
@@ -805,19 +805,19 @@
         <v>20</v>
       </c>
       <c r="AE2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI2" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="AF2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AH2" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI2" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
